--- a/Convert_from_xlsx_to_Json/table_normalization/employment-table14.xlsx
+++ b/Convert_from_xlsx_to_Json/table_normalization/employment-table14.xlsx
@@ -226,9 +226,9 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -535,7 +535,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -550,26 +550,26 @@
       <c r="I1" s="1"/>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="3"/>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="1"/>
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1" t="s">
+      <c r="C2" s="2"/>
+      <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1" t="s">
+      <c r="E2" s="2"/>
+      <c r="F2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1" t="s">
+      <c r="G2" s="2"/>
+      <c r="H2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="1"/>
+      <c r="I2" s="2"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="3"/>
+      <c r="A3" s="1"/>
       <c r="B3">
         <v>2022</v>
       </c>
@@ -688,7 +688,7 @@
       </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
     </row>
     <row r="40" spans="1:9">
-      <c r="A40" s="2" t="s">
+      <c r="A40" s="3" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1781,7 +1781,7 @@
       </c>
     </row>
     <row r="52" spans="1:9">
-      <c r="A52" s="2" t="s">
+      <c r="A52" s="3" t="s">
         <v>49</v>
       </c>
     </row>
